--- a/exports/TRENT_full_report.xlsx
+++ b/exports/TRENT_full_report.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q59"/>
+  <dimension ref="A1:Q60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="C59" s="1" t="n">
@@ -3782,13 +3782,21 @@
       <c r="F59" t="n">
         <v>6.95</v>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" s="1" t="n">
+        <v>46322.55208333334</v>
+      </c>
+      <c r="H59" t="n">
+        <v>2825</v>
+      </c>
       <c r="I59" t="n">
         <v>2859.569834563187</v>
       </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="J59" s="2" t="n">
+        <v>6.166666666666667</v>
+      </c>
+      <c r="K59" t="n">
+        <v>-0.51</v>
+      </c>
       <c r="L59" t="n">
         <v>3.01</v>
       </c>
@@ -3796,7 +3804,7 @@
         <v>0.11</v>
       </c>
       <c r="N59" t="n">
-        <v>1.98</v>
+        <v>2.69</v>
       </c>
       <c r="O59" t="n">
         <v>-2.48</v>
@@ -3806,6 +3814,55 @@
       </c>
       <c r="Q59" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>UP</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>46323.38541666666</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2877.1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2669.167519388784</v>
+      </c>
+      <c r="F60" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="n">
+        <v>2721.975767449905</v>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="n">
+        <v>3</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P60" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5828,16 +5885,16 @@
         <v>2545.8</v>
       </c>
       <c r="E59" t="n">
-        <v>2805.6</v>
+        <v>2897.8</v>
       </c>
       <c r="F59" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G59" t="n">
         <v>17.55</v>
       </c>
       <c r="H59" t="n">
-        <v>7.29</v>
+        <v>10.81</v>
       </c>
       <c r="I59" t="n">
         <v>14.9</v>
@@ -5879,7 +5936,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
@@ -5899,7 +5956,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -5909,7 +5966,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29.6</v>
+        <v>29.2</v>
       </c>
     </row>
     <row r="6">
@@ -5919,7 +5976,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.2</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="7">
@@ -5949,7 +6006,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38.2</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="10">
@@ -5959,7 +6016,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54.5</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="11">
@@ -5969,7 +6026,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12">
@@ -5989,7 +6046,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>70.2</v>
+        <v>70.7</v>
       </c>
     </row>
     <row r="14">
@@ -5999,7 +6056,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.25</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="15">
@@ -6019,7 +6076,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="17">
@@ -6039,7 +6096,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>56.1</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="19">
@@ -6049,7 +6106,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.62</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="20">
@@ -6059,7 +6116,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.66</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="21">
@@ -6099,7 +6156,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="25">
@@ -6119,7 +6176,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="27">

--- a/exports/TRENT_full_report.xlsx
+++ b/exports/TRENT_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q60"/>
+  <dimension ref="A1:U60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,25 +557,25 @@
         <v>4.97</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44585.55208333334</v>
+        <v>44586.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>745.3</v>
+        <v>723.9</v>
       </c>
       <c r="I2" t="n">
         <v>736.63405225418</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K2" t="n">
-        <v>3.43</v>
+        <v>0.46</v>
       </c>
       <c r="L2" t="n">
-        <v>1.65</v>
+        <v>2.82</v>
       </c>
       <c r="M2" t="n">
-        <v>1.43</v>
+        <v>2.32</v>
       </c>
       <c r="N2" t="n">
         <v>5.66</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>11.11</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44620.38541666666</v>
+        <v>44620.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>720.4</v>
+        <v>741.3</v>
       </c>
       <c r="I3" t="n">
         <v>733.2278908691155</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K3" t="n">
-        <v>0.48</v>
+        <v>-2.4</v>
       </c>
       <c r="L3" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="M3" t="n">
         <v>2.6</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>10.7</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44662.55208333334</v>
+        <v>44663.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>853.2</v>
+        <v>831.9</v>
       </c>
       <c r="I4" t="n">
         <v>832.3425038699284</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>42</v>
+        <v>42.83333333333334</v>
       </c>
       <c r="K4" t="n">
-        <v>15.1</v>
+        <v>12.22</v>
       </c>
       <c r="L4" t="n">
         <v>6.48</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>8.130000000000001</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44712.38541666666</v>
+        <v>44712.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>750.4</v>
+        <v>751.7</v>
       </c>
       <c r="I5" t="n">
         <v>751.0531331560467</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>49</v>
+        <v>49.16666666666666</v>
       </c>
       <c r="K5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="L5" t="n">
         <v>3.77</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>8.32</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44729.38541666666</v>
+        <v>44729.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>705.3</v>
+        <v>692.1</v>
       </c>
       <c r="I6" t="n">
         <v>702.4060746481204</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>16.83333333333333</v>
+        <v>17</v>
       </c>
       <c r="K6" t="n">
-        <v>-6.17</v>
+        <v>-7.93</v>
       </c>
       <c r="L6" t="n">
-        <v>6.17</v>
+        <v>8.09</v>
       </c>
       <c r="M6" t="n">
         <v>0.6899999999999999</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>8.83</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44741.38541666666</v>
+        <v>44741.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>724.6</v>
+        <v>734.7</v>
       </c>
       <c r="I7" t="n">
         <v>732.7655102136437</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>11.83333333333333</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.7</v>
+        <v>-6.16</v>
       </c>
       <c r="L7" t="n">
-        <v>4.72</v>
+        <v>7.4</v>
       </c>
       <c r="M7" t="n">
         <v>1.98</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>7.6</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>930.4</v>
+        <v>893</v>
       </c>
       <c r="I8" t="n">
         <v>923.1971948624968</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>51</v>
+        <v>53.83333333333334</v>
       </c>
       <c r="K8" t="n">
-        <v>26.64</v>
+        <v>21.55</v>
       </c>
       <c r="L8" t="n">
         <v>3.89</v>
@@ -897,7 +992,7 @@
         <v>1.15</v>
       </c>
       <c r="N8" t="n">
-        <v>4.28</v>
+        <v>5.71</v>
       </c>
       <c r="O8" t="n">
         <v>3</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>11.47</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44817.38541666666</v>
+        <v>44817.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>952.3</v>
+        <v>974.6</v>
       </c>
       <c r="I9" t="n">
         <v>958.2695729650799</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K9" t="n">
-        <v>-6.64</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>7.87</v>
+        <v>9.74</v>
       </c>
       <c r="M9" t="n">
         <v>1.19</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>6.54</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44832.55208333334</v>
+        <v>44833.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>921.3</v>
+        <v>916.7</v>
       </c>
       <c r="I10" t="n">
         <v>920.1445141284358</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>-5.47</v>
+        <v>-5.94</v>
       </c>
       <c r="L10" t="n">
         <v>7.37</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>8.77</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44861.38541666666</v>
+        <v>44861.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>958.7</v>
+        <v>977.7</v>
       </c>
       <c r="I11" t="n">
         <v>973.7826063342416</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.58</v>
+        <v>-6.65</v>
       </c>
       <c r="L11" t="n">
         <v>7.63</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>6.32</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44875.55208333334</v>
+        <v>44876.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>986.5</v>
+        <v>934.4</v>
       </c>
       <c r="I12" t="n">
         <v>974.2484555473206</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>0.9</v>
+        <v>-4.43</v>
       </c>
       <c r="L12" t="n">
-        <v>2.08</v>
+        <v>4.88</v>
       </c>
       <c r="M12" t="n">
         <v>0.67</v>
       </c>
       <c r="N12" t="n">
-        <v>2.86</v>
+        <v>4.22</v>
       </c>
       <c r="O12" t="n">
         <v>2.34</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>10.69</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44893.55208333334</v>
+        <v>44894.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>958.3</v>
+        <v>969.2</v>
       </c>
       <c r="I13" t="n">
         <v>965.059410949249</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.56</v>
+        <v>-3.72</v>
       </c>
       <c r="L13" t="n">
         <v>7.13</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>4.8</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44910.55208333334</v>
+        <v>44911.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>955.3</v>
+        <v>944.5</v>
       </c>
       <c r="I14" t="n">
         <v>945.7128752110657</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.43</v>
+        <v>-2.55</v>
       </c>
       <c r="L14" t="n">
-        <v>1.76</v>
+        <v>3.63</v>
       </c>
       <c r="M14" t="n">
         <v>0.55</v>
       </c>
       <c r="N14" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="O14" t="n">
         <v>1</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,25 +1454,25 @@
         <v>4.27</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44956.55208333334</v>
+        <v>44958.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>786.7</v>
+        <v>839.1</v>
       </c>
       <c r="I15" t="n">
         <v>826.67165353212</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K15" t="n">
-        <v>16.71</v>
+        <v>11.16</v>
       </c>
       <c r="L15" t="n">
         <v>1.1</v>
       </c>
       <c r="M15" t="n">
-        <v>0.77</v>
+        <v>2.03</v>
       </c>
       <c r="N15" t="n">
         <v>5.14</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>9.390000000000001</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44981.55208333334</v>
+        <v>44984.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>868.7</v>
+        <v>849.3</v>
       </c>
       <c r="I16" t="n">
         <v>859.0825905860401</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K16" t="n">
-        <v>3.53</v>
+        <v>1.22</v>
       </c>
       <c r="L16" t="n">
         <v>5.28</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>6.78</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45002.38541666666</v>
+        <v>45002.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>894.2</v>
+        <v>903</v>
       </c>
       <c r="I17" t="n">
         <v>902.3147971293697</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.29</v>
+        <v>-6.32</v>
       </c>
       <c r="L17" t="n">
         <v>7.3</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>5.83</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45113.55208333334</v>
+        <v>45114.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>1166.2</v>
+        <v>1138.4</v>
       </c>
       <c r="I18" t="n">
         <v>1138.55018119491</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>111</v>
+        <v>111.8333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>29.15</v>
+        <v>26.07</v>
       </c>
       <c r="L18" t="n">
         <v>4.91</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>147</v>
+        <v>148</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>6.32</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45138.38541666666</v>
+        <v>45138.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>1166</v>
+        <v>1173.3</v>
       </c>
       <c r="I19" t="n">
         <v>1170.720398219349</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.42</v>
+        <v>-3.07</v>
       </c>
       <c r="L19" t="n">
         <v>3.3</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.4</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45202.55208333334</v>
+        <v>45203.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>1371.8</v>
+        <v>1348.8</v>
       </c>
       <c r="I20" t="n">
         <v>1354.852310199899</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>64</v>
+        <v>64.83333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>16.92</v>
+        <v>14.96</v>
       </c>
       <c r="L20" t="n">
         <v>5.09</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>6.33</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45225.55208333334</v>
+        <v>45226.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>1356.7</v>
+        <v>1419</v>
       </c>
       <c r="I21" t="n">
         <v>1385.884403607236</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.59</v>
+        <v>-5.2</v>
       </c>
       <c r="L21" t="n">
-        <v>4.66</v>
+        <v>5.92</v>
       </c>
       <c r="M21" t="n">
         <v>1.16</v>
       </c>
       <c r="N21" t="n">
-        <v>2.58</v>
+        <v>4.1</v>
       </c>
       <c r="O21" t="n">
         <v>-1.69</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>8.09</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45321.38541666666</v>
+        <v>45321.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>2094.4</v>
+        <v>2029.7</v>
       </c>
       <c r="I22" t="n">
         <v>2063.96807290237</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>95</v>
+        <v>95.16666666666667</v>
       </c>
       <c r="K22" t="n">
-        <v>47.6</v>
+        <v>43.04</v>
       </c>
       <c r="L22" t="n">
         <v>4.57</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>7.84</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45329.38541666666</v>
+        <v>45329.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>2152</v>
+        <v>2418.7</v>
       </c>
       <c r="I23" t="n">
         <v>2169.388720458754</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K23" t="n">
-        <v>-6.03</v>
+        <v>-19.17</v>
       </c>
       <c r="L23" t="n">
-        <v>9.470000000000001</v>
+        <v>19.38</v>
       </c>
       <c r="M23" t="n">
         <v>1.84</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>16.53</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45489.55208333334</v>
+        <v>45491.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>3761.3</v>
+        <v>3570.9</v>
       </c>
       <c r="I24" t="n">
         <v>3636.621187102004</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>160</v>
+        <v>161.8333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>55.51</v>
+        <v>47.64</v>
       </c>
       <c r="L24" t="n">
         <v>11.09</v>
@@ -1809,7 +2096,7 @@
         <v>2.85</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>5.71</v>
       </c>
       <c r="O24" t="n">
         <v>19.34</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>213</v>
+        <v>214</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>6</v>
+      </c>
+      <c r="U24" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45502.38541666666</v>
+        <v>45502.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>3647.3</v>
+        <v>3673.3</v>
       </c>
       <c r="I25" t="n">
         <v>3658.388278489313</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.14</v>
+        <v>-2.87</v>
       </c>
       <c r="L25" t="n">
         <v>5.67</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,25 +2213,25 @@
         <v>6.35</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>3693.3</v>
+        <v>3554.1</v>
       </c>
       <c r="I26" t="n">
         <v>3646.079844238968</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>4</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>0.54</v>
+        <v>-3.25</v>
       </c>
       <c r="L26" t="n">
-        <v>1.08</v>
+        <v>5.15</v>
       </c>
       <c r="M26" t="n">
-        <v>0.71</v>
+        <v>3.25</v>
       </c>
       <c r="N26" t="n">
         <v>3.92</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>7.98</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45512.55208333334</v>
+        <v>45513.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>3762.7</v>
+        <v>4110.7</v>
       </c>
       <c r="I27" t="n">
         <v>3788.435187054217</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K27" t="n">
-        <v>-5.87</v>
+        <v>-15.66</v>
       </c>
       <c r="L27" t="n">
-        <v>7.43</v>
+        <v>16</v>
       </c>
       <c r="M27" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="N27" t="n">
-        <v>5.27</v>
+        <v>11.98</v>
       </c>
       <c r="O27" t="n">
         <v>-3.34</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>13.24</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45568.55208333334</v>
+        <v>45569.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>4980</v>
+        <v>4936.4</v>
       </c>
       <c r="I28" t="n">
         <v>4972.672844560062</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>55.16666666666666</v>
+        <v>56</v>
       </c>
       <c r="K28" t="n">
-        <v>21.15</v>
+        <v>20.09</v>
       </c>
       <c r="L28" t="n">
         <v>8.75</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>5.13</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45572.55208333334</v>
+        <v>45573.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>4993.3</v>
+        <v>5275.9</v>
       </c>
       <c r="I29" t="n">
         <v>5189.709262609269</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.15</v>
+        <v>-6.88</v>
       </c>
       <c r="L29" t="n">
-        <v>1.34</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>0.01</v>
+        <v>0.4</v>
       </c>
       <c r="N29" t="n">
-        <v>1.23</v>
+        <v>7.37</v>
       </c>
       <c r="O29" t="n">
         <v>-0.95</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>9.5</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45582.38541666666</v>
+        <v>45582.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>5210.2</v>
+        <v>5154.2</v>
       </c>
       <c r="I30" t="n">
         <v>5159.621779629129</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.25</v>
+        <v>-2.31</v>
       </c>
       <c r="L30" t="n">
         <v>5.85</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>7.07</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45631.38541666666</v>
+        <v>45631.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>4567.6</v>
+        <v>4699.3</v>
       </c>
       <c r="I31" t="n">
         <v>4589.248919816023</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>48.83333333333334</v>
+        <v>49</v>
       </c>
       <c r="K31" t="n">
-        <v>11.38</v>
+        <v>8.83</v>
       </c>
       <c r="L31" t="n">
         <v>1.53</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>7.76</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45663.38541666666</v>
+        <v>45663.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>4692.3</v>
+        <v>4646.7</v>
       </c>
       <c r="I32" t="n">
         <v>4650.066964311445</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>31.83333333333333</v>
+        <v>32</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.15</v>
+        <v>-1.12</v>
       </c>
       <c r="L32" t="n">
         <v>3.68</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>6.93</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45688.55208333334</v>
+        <v>45689.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>3843.3</v>
+        <v>4054.7</v>
       </c>
       <c r="I33" t="n">
         <v>3900.884449659164</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>25</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K33" t="n">
-        <v>17.29</v>
+        <v>12.74</v>
       </c>
       <c r="L33" t="n">
         <v>1.65</v>
@@ -2322,7 +2717,7 @@
         <v>1.55</v>
       </c>
       <c r="N33" t="n">
-        <v>4.1</v>
+        <v>6.77</v>
       </c>
       <c r="O33" t="n">
         <v>-4.32</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,25 +2765,25 @@
         <v>11.82</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45694.38541666666</v>
+        <v>45694.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>3780</v>
+        <v>3512.7</v>
       </c>
       <c r="I34" t="n">
         <v>3735.528507318751</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>5</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="K34" t="n">
-        <v>-6.77</v>
+        <v>-13.37</v>
       </c>
       <c r="L34" t="n">
-        <v>8.199999999999999</v>
+        <v>13.76</v>
       </c>
       <c r="M34" t="n">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="N34" t="n">
         <v>8.359999999999999</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>17.62</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45733.38541666666</v>
+        <v>45733.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>3430.8</v>
+        <v>3434.3</v>
       </c>
       <c r="I35" t="n">
         <v>3433.576493045205</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>38.83333333333334</v>
+        <v>39</v>
       </c>
       <c r="K35" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="L35" t="n">
         <v>9.220000000000001</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>6.59</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>3711.9</v>
+        <v>3137.3</v>
       </c>
       <c r="I36" t="n">
         <v>3541.116469973853</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>18</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>8.08</v>
+        <v>-8.65</v>
       </c>
       <c r="L36" t="n">
-        <v>2.07</v>
+        <v>12.88</v>
       </c>
       <c r="M36" t="n">
-        <v>0.01</v>
+        <v>10.08</v>
       </c>
       <c r="N36" t="n">
-        <v>2.01</v>
+        <v>14.69</v>
       </c>
       <c r="O36" t="n">
         <v>2.6</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>14.59</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45764.55208333334</v>
+        <v>45768.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>3411.7</v>
+        <v>3541</v>
       </c>
       <c r="I37" t="n">
         <v>3431.682483230306</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K37" t="n">
-        <v>-8.75</v>
+        <v>-12.87</v>
       </c>
       <c r="L37" t="n">
-        <v>9.31</v>
+        <v>13.3</v>
       </c>
       <c r="M37" t="n">
         <v>3.39</v>
       </c>
       <c r="N37" t="n">
-        <v>3.44</v>
+        <v>4.58</v>
       </c>
       <c r="O37" t="n">
         <v>-14.69</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>9.94</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45820.38541666666</v>
+        <v>45820.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>3829</v>
+        <v>3746.7</v>
       </c>
       <c r="I38" t="n">
         <v>3757.562326696385</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>52</v>
+        <v>52.16666666666666</v>
       </c>
       <c r="K38" t="n">
-        <v>8.130000000000001</v>
+        <v>5.81</v>
       </c>
       <c r="L38" t="n">
         <v>4.67</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>6.01</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45828.38541666666</v>
+        <v>45828.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>3847.3</v>
+        <v>3966.7</v>
       </c>
       <c r="I39" t="n">
         <v>3887.948282799332</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K39" t="n">
-        <v>-2.69</v>
+        <v>-5.87</v>
       </c>
       <c r="L39" t="n">
-        <v>3.43</v>
+        <v>7.29</v>
       </c>
       <c r="M39" t="n">
         <v>1.26</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>6.41</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45841.55208333334</v>
+        <v>45842.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>4120</v>
+        <v>3674.7</v>
       </c>
       <c r="I40" t="n">
         <v>3922.651346152685</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K40" t="n">
-        <v>3.86</v>
+        <v>-7.36</v>
       </c>
       <c r="L40" t="n">
-        <v>3.19</v>
+        <v>10.08</v>
       </c>
       <c r="M40" t="n">
-        <v>1.68</v>
+        <v>8.17</v>
       </c>
       <c r="N40" t="n">
-        <v>1.06</v>
+        <v>11.25</v>
       </c>
       <c r="O40" t="n">
         <v>4.2</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,25 +3248,25 @@
         <v>10.82</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45870.55208333334</v>
+        <v>45873.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>3452.7</v>
+        <v>3504.3</v>
       </c>
       <c r="I41" t="n">
         <v>3489.244041546308</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K41" t="n">
-        <v>6.04</v>
+        <v>4.64</v>
       </c>
       <c r="L41" t="n">
         <v>4.95</v>
       </c>
       <c r="M41" t="n">
-        <v>0.64</v>
+        <v>1.85</v>
       </c>
       <c r="N41" t="n">
         <v>3.09</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>6.13</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45897.38541666666</v>
+        <v>45897.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>3507</v>
+        <v>3499</v>
       </c>
       <c r="I42" t="n">
         <v>3506.365607429751</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K42" t="n">
-        <v>0.08</v>
+        <v>-0.15</v>
       </c>
       <c r="L42" t="n">
         <v>1.79</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,25 +3386,25 @@
         <v>4.49</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45903.55208333334</v>
+        <v>45904.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>3646.7</v>
+        <v>3717.3</v>
       </c>
       <c r="I43" t="n">
         <v>3655.954338477201</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K43" t="n">
-        <v>-4.22</v>
+        <v>-6.24</v>
       </c>
       <c r="L43" t="n">
-        <v>4.79</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>0.55</v>
+        <v>1</v>
       </c>
       <c r="N43" t="n">
         <v>2.89</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>5.14</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45908.55208333334</v>
+        <v>45909.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>3538.7</v>
+        <v>3475.3</v>
       </c>
       <c r="I44" t="n">
         <v>3526.276339873491</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K44" t="n">
-        <v>-4.8</v>
+        <v>-6.51</v>
       </c>
       <c r="L44" t="n">
-        <v>4.95</v>
+        <v>6.63</v>
       </c>
       <c r="M44" t="n">
         <v>0.03</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>7.26</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46013.38541666666</v>
+        <v>46013.55208333334</v>
       </c>
       <c r="H45" t="n">
-        <v>2770.2</v>
+        <v>2812.7</v>
       </c>
       <c r="I45" t="n">
         <v>2783.562237333467</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>104</v>
+        <v>104.1666666666667</v>
       </c>
       <c r="K45" t="n">
-        <v>20.29</v>
+        <v>19.07</v>
       </c>
       <c r="L45" t="n">
         <v>2.57</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>142</v>
+        <v>143</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>4.85</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46027.55208333334</v>
+        <v>46028.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>2944.7</v>
+        <v>2730</v>
       </c>
       <c r="I46" t="n">
         <v>2828.67887073437</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K46" t="n">
-        <v>4.69</v>
+        <v>-2.94</v>
       </c>
       <c r="L46" t="n">
-        <v>1.71</v>
+        <v>3.77</v>
       </c>
       <c r="M46" t="n">
-        <v>0.04</v>
+        <v>4.73</v>
       </c>
       <c r="N46" t="n">
-        <v>1.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O46" t="n">
         <v>3.82</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>7.6</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46056.55208333334</v>
+        <v>46057.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>2546.8</v>
+        <v>2638.1</v>
       </c>
       <c r="I47" t="n">
         <v>2602.371957323999</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K47" t="n">
-        <v>6.71</v>
+        <v>3.37</v>
       </c>
       <c r="L47" t="n">
         <v>2.77</v>
@@ -3120,7 +3683,7 @@
         <v>4.78</v>
       </c>
       <c r="N47" t="n">
-        <v>2.64</v>
+        <v>5.26</v>
       </c>
       <c r="O47" t="n">
         <v>-8.199999999999999</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.279999999999999</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46073.55208333334</v>
+        <v>46076.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>2723.3</v>
+        <v>2695.8</v>
       </c>
       <c r="I48" t="n">
         <v>2701.780261167465</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K48" t="n">
-        <v>3.23</v>
+        <v>2.19</v>
       </c>
       <c r="L48" t="n">
         <v>3.84</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>5.92</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46114.55208333334</v>
+        <v>46118.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>2355.3</v>
+        <v>2528.5</v>
       </c>
       <c r="I49" t="n">
         <v>2367.363581383937</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K49" t="n">
-        <v>12.63</v>
+        <v>6.21</v>
       </c>
       <c r="L49" t="n">
         <v>1.88</v>
@@ -3234,7 +3821,7 @@
         <v>4.5</v>
       </c>
       <c r="N49" t="n">
-        <v>6.71</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="O49" t="n">
         <v>-0.73</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>11.28</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46142.55208333334</v>
+        <v>46146.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>2765.3</v>
+        <v>2725.1</v>
       </c>
       <c r="I50" t="n">
         <v>2762.535591999969</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K50" t="n">
-        <v>9.369999999999999</v>
+        <v>7.78</v>
       </c>
       <c r="L50" t="n">
         <v>4.16</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>7.55</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46163.55208333334</v>
+        <v>46164.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>2781.9</v>
+        <v>2856</v>
       </c>
       <c r="I51" t="n">
         <v>2827.066746451861</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.08</v>
+        <v>-4.8</v>
       </c>
       <c r="L51" t="n">
         <v>6.54</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>6.81</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46181.38541666666</v>
+        <v>46181.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>2760.2</v>
+        <v>2711.9</v>
       </c>
       <c r="I52" t="n">
         <v>2747.197801974331</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.35</v>
+        <v>-5.05</v>
       </c>
       <c r="L52" t="n">
         <v>5.34</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>7.76</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>2756</v>
+        <v>2906.3</v>
       </c>
       <c r="I53" t="n">
         <v>2892.182367068463</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>4</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>-1.63</v>
+        <v>-7.17</v>
       </c>
       <c r="L53" t="n">
-        <v>4.93</v>
+        <v>7.19</v>
       </c>
       <c r="M53" t="n">
         <v>1.36</v>
       </c>
       <c r="N53" t="n">
-        <v>2.02</v>
+        <v>5.29</v>
       </c>
       <c r="O53" t="n">
         <v>-2.1</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>8.84</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46209.55208333334</v>
+        <v>46210.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>3340.1</v>
+        <v>2932.5</v>
       </c>
       <c r="I54" t="n">
         <v>3189.352109367874</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K54" t="n">
-        <v>14.93</v>
+        <v>0.9</v>
       </c>
       <c r="L54" t="n">
         <v>3.96</v>
       </c>
       <c r="M54" t="n">
-        <v>0.12</v>
+        <v>7.79</v>
       </c>
       <c r="N54" t="n">
-        <v>1.28</v>
+        <v>12.56</v>
       </c>
       <c r="O54" t="n">
         <v>5.29</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>11.39</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46231.55208333334</v>
+        <v>46232.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>2930</v>
+        <v>2999.5</v>
       </c>
       <c r="I55" t="n">
         <v>2974.434999874881</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K55" t="n">
-        <v>0.09</v>
+        <v>-2.28</v>
       </c>
       <c r="L55" t="n">
         <v>5.03</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.58</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46246.38541666666</v>
+        <v>46246.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>2991.5</v>
+        <v>2982.1</v>
       </c>
       <c r="I56" t="n">
         <v>2986.535053867152</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.27</v>
+        <v>-0.58</v>
       </c>
       <c r="L56" t="n">
         <v>2.77</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>4.97</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46300.55208333334</v>
+        <v>46301.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>2580</v>
+        <v>2881</v>
       </c>
       <c r="I57" t="n">
         <v>2689.90054184691</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>54</v>
+        <v>54.83333333333334</v>
       </c>
       <c r="K57" t="n">
-        <v>13.48</v>
+        <v>3.39</v>
       </c>
       <c r="L57" t="n">
         <v>1.29</v>
       </c>
       <c r="M57" t="n">
-        <v>0.95</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="N57" t="n">
-        <v>2.06</v>
+        <v>12.44</v>
       </c>
       <c r="O57" t="n">
         <v>-0.89</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>8.33</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46314.55208333334</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>2881.4</v>
+        <v>2810.8</v>
       </c>
       <c r="I58" t="n">
         <v>2818.730525854553</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K58" t="n">
-        <v>0.01</v>
+        <v>-2.44</v>
       </c>
       <c r="L58" t="n">
         <v>3.43</v>
@@ -3747,7 +4442,7 @@
         <v>0.6</v>
       </c>
       <c r="N58" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="O58" t="n">
         <v>12.44</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,25 +4490,25 @@
         <v>6.95</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46322.55208333334</v>
+        <v>46323.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>2825</v>
+        <v>2877.1</v>
       </c>
       <c r="I59" t="n">
         <v>2859.569834563187</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.51</v>
+        <v>-2.36</v>
       </c>
       <c r="L59" t="n">
         <v>3.01</v>
       </c>
       <c r="M59" t="n">
-        <v>0.11</v>
+        <v>0.35</v>
       </c>
       <c r="N59" t="n">
         <v>2.69</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3864,6 +4583,12 @@
       <c r="Q60" t="n">
         <v>2</v>
       </c>
+      <c r="R60" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5966,7 +6691,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29.2</v>
+        <v>30.2</v>
       </c>
     </row>
     <row r="6">
@@ -5976,7 +6701,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.6</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="7">
@@ -5986,7 +6711,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>161.8</v>
       </c>
     </row>
     <row r="8">
@@ -5996,7 +6721,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -6006,7 +6731,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37.1</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="10">
@@ -6016,7 +6741,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54.4</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="11">
@@ -6026,7 +6751,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
@@ -6036,7 +6761,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -6046,7 +6771,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>70.7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14">
@@ -6056,7 +6781,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.15</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="15">
@@ -6066,7 +6791,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.390000000000001</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="16">
@@ -6076,7 +6801,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.91</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="17">
@@ -6086,7 +6811,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>55.51</v>
+        <v>47.64</v>
       </c>
     </row>
     <row r="18">
@@ -6096,7 +6821,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55.2</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="19">
@@ -6106,7 +6831,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.6</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="20">
@@ -6116,7 +6841,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.62</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="21">
@@ -6126,7 +6851,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11.09</v>
+        <v>19.38</v>
       </c>
     </row>
     <row r="22">
@@ -6136,7 +6861,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23">
@@ -6146,7 +6871,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -6156,7 +6881,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.28</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="25">
@@ -6166,7 +6891,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.78</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="26">
@@ -6176,7 +6901,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.69</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="27">
@@ -6196,7 +6921,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
